--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0001T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.26851932144415</v>
+        <v>4.431134389734674</v>
       </c>
       <c r="D2" t="n">
-        <v>27.35721303915454</v>
+        <v>4.445547118862613</v>
       </c>
       <c r="E2" t="n">
-        <v>8.027600689523773</v>
+        <v>1.304485112047613</v>
       </c>
       <c r="F2" t="n">
-        <v>7.443230389240822</v>
+        <v>1.209524938251634</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.01461727979517</v>
+        <v>6.502375307966715</v>
       </c>
       <c r="D3" t="n">
-        <v>39.81610999426888</v>
+        <v>6.470117874068693</v>
       </c>
       <c r="E3" t="n">
-        <v>8.027600689523773</v>
+        <v>1.304485112047613</v>
       </c>
       <c r="F3" t="n">
-        <v>7.443230389240822</v>
+        <v>1.209524938251634</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.62183912269282</v>
+        <v>6.276048857437583</v>
       </c>
       <c r="D4" t="n">
-        <v>38.41692083127086</v>
+        <v>6.242749635081516</v>
       </c>
       <c r="E4" t="n">
-        <v>8.027600689523773</v>
+        <v>1.304485112047613</v>
       </c>
       <c r="F4" t="n">
-        <v>7.443230389240822</v>
+        <v>1.209524938251634</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.42454903586932</v>
+        <v>3.318989218328765</v>
       </c>
       <c r="D5" t="n">
-        <v>20.28841084246057</v>
+        <v>3.296866761899843</v>
       </c>
       <c r="E5" t="n">
-        <v>8.027600689523773</v>
+        <v>1.304485112047613</v>
       </c>
       <c r="F5" t="n">
-        <v>7.443230389240822</v>
+        <v>1.209524938251634</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.26543157512949</v>
+        <v>4.755632630958543</v>
       </c>
       <c r="D6" t="n">
-        <v>28.80998990094666</v>
+        <v>4.681623358903833</v>
       </c>
       <c r="E6" t="n">
-        <v>8.027600689523773</v>
+        <v>1.304485112047613</v>
       </c>
       <c r="F6" t="n">
-        <v>7.443230389240822</v>
+        <v>1.209524938251634</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.15163310013351</v>
+        <v>5.062140378771696</v>
       </c>
       <c r="D7" t="n">
-        <v>30.95619823395624</v>
+        <v>5.03038221301789</v>
       </c>
       <c r="E7" t="n">
-        <v>8.027600689523773</v>
+        <v>1.304485112047613</v>
       </c>
       <c r="F7" t="n">
-        <v>7.443230389240822</v>
+        <v>1.209524938251634</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.55347853226841</v>
+        <v>4.314940261493617</v>
       </c>
       <c r="D8" t="n">
-        <v>26.20728858534666</v>
+        <v>4.258684395118832</v>
       </c>
       <c r="E8" t="n">
-        <v>8.027600689523773</v>
+        <v>1.304485112047613</v>
       </c>
       <c r="F8" t="n">
-        <v>7.443230389240822</v>
+        <v>1.209524938251634</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.54720117266299</v>
+        <v>2.363920190557736</v>
       </c>
       <c r="D9" t="n">
-        <v>14.79536390557341</v>
+        <v>2.404246634655679</v>
       </c>
       <c r="E9" t="n">
-        <v>8.027600689523773</v>
+        <v>1.304485112047613</v>
       </c>
       <c r="F9" t="n">
-        <v>7.443230389240822</v>
+        <v>1.209524938251634</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>19.47277509791094</v>
+        <v>3.164325953410527</v>
       </c>
       <c r="D10" t="n">
-        <v>30.58227750081405</v>
+        <v>4.969620093882283</v>
       </c>
       <c r="E10" t="n">
-        <v>8.027600689523773</v>
+        <v>1.304485112047613</v>
       </c>
       <c r="F10" t="n">
-        <v>7.443230389240822</v>
+        <v>1.209524938251634</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
